--- a/ig/main/CodeSystem-tre-r389-statut-bilan-projet-personnalise.xlsx
+++ b/ig/main/CodeSystem-tre-r389-statut-bilan-projet-personnalise.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Properties" r:id="rId4" sheetId="2"/>
-    <sheet name="Concepts" r:id="rId5" sheetId="3"/>
+    <sheet name="Filters" r:id="rId5" sheetId="3"/>
+    <sheet name="Concepts" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="69">
   <si>
     <t>Property</t>
   </si>
@@ -185,6 +186,12 @@
   </si>
   <si>
     <t>Date de retrait du code</t>
+  </si>
+  <si>
+    <t>Operators</t>
+  </si>
+  <si>
+    <t>=</t>
   </si>
   <si>
     <t>Level</t>
@@ -628,56 +635,92 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2"/>
     </row>
